--- a/dxf/assets/eia_list_template.xlsx
+++ b/dxf/assets/eia_list_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,16 @@
       <c r="I1" t="str">
         <v>평가서 공개유무</v>
       </c>
+      <c r="J1" t="str">
+        <v>광역자치단체</v>
+      </c>
+      <c r="K1" t="str">
+        <v>기초자치단체</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dxf/assets/eia_list_template.xlsx
+++ b/dxf/assets/eia_list_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,10 +433,13 @@
       <c r="K1" t="str">
         <v>기초자치단체</v>
       </c>
+      <c r="L1" t="str">
+        <v>사업자명</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>